--- a/data/eval/ques.xlsx
+++ b/data/eval/ques.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\.vscode\TT\1\data\eval\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\.vscode\TT\TN\data\eval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5027D90B-0C6E-46DE-AEA4-16BB9292B908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CCA50DB-1CA9-483B-A9B9-F15625A2C4CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8976" yWindow="516" windowWidth="13524" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="49">
   <si>
     <t>id</t>
   </si>
@@ -154,6 +154,24 @@
   </si>
   <si>
     <t>Lộ trình áp dụng toàn bộ các hình thức giao dịch điện tử trong lĩnh vực quản lý thuế phải bảo đảm hoàn thành trước thời điểm nào?</t>
+  </si>
+  <si>
+    <t>question_type</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t>answerable</t>
+  </si>
+  <si>
+    <t>notes</t>
   </si>
 </sst>
 </file>
@@ -477,14 +495,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="20.109375" customWidth="1"/>
     <col min="8" max="8" width="11.88671875" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -509,8 +528,17 @@
       <c r="H1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -530,10 +558,16 @@
         <v>2</v>
       </c>
       <c r="H2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -553,10 +587,16 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -576,10 +616,16 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -599,10 +645,16 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -622,10 +674,16 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -645,10 +703,16 @@
         <v>2</v>
       </c>
       <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -668,10 +732,16 @@
         <v>2</v>
       </c>
       <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -691,10 +761,16 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -714,10 +790,16 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -737,10 +819,16 @@
         <v>2</v>
       </c>
       <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -760,10 +848,16 @@
         <v>2</v>
       </c>
       <c r="H12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -783,10 +877,16 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I13" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -806,10 +906,16 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -829,10 +935,16 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -852,10 +964,16 @@
         <v>31</v>
       </c>
       <c r="H16" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -875,10 +993,16 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>33</v>
       </c>
@@ -886,7 +1010,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>17</v>
       </c>
@@ -906,10 +1030,16 @@
         <v>2</v>
       </c>
       <c r="H19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>14</v>
       </c>
@@ -923,7 +1053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>18</v>
       </c>
@@ -936,8 +1066,14 @@
       <c r="D21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H21" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>19</v>
       </c>
@@ -956,8 +1092,14 @@
       <c r="F22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>20</v>
       </c>
@@ -976,8 +1118,14 @@
       <c r="F23">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>21</v>
       </c>
@@ -996,8 +1144,14 @@
       <c r="F24">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>22</v>
       </c>
@@ -1015,10 +1169,17 @@
       </c>
       <c r="F25">
         <v>4</v>
+      </c>
+      <c r="H25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>